--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -435,71 +435,49 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t>##var#column</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>initialGold</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>initialInterestCap</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>initialFoodAdjustCount</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>interestThreshold</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>interestGoldPer</t>
-        </is>
-      </c>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>##comment</t>
+          <t>initialGold</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t>初始金币</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>利息节点单次最高可获得金币数</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>初始食物调整次数</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Interest:每满该金币阈值</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Interest:每档获得金币</t>
-        </is>
-      </c>
+      <c r="D2" s="1" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t>initialInterestCap</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -509,39 +487,72 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
+          <t>利息节点单次最高可获得金币数</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" t="n">
-        <v>9999</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>initialFoodAdjustCount</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>初始食物调整次数</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>interestThreshold</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Interest:每满该金币阈值</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>interestGoldPer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Interest:每档获得金币</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -1,47 +1,446 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="game_base" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+  <si>
+    <t>##var#column</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>initialGold</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>初始金币</t>
+  </si>
+  <si>
+    <t>initialInterestCap</t>
+  </si>
+  <si>
+    <t>利息节点单次最高可获得金币数</t>
+  </si>
+  <si>
+    <t>initialFoodAdjustCount</t>
+  </si>
+  <si>
+    <t>初始食物调整次数</t>
+  </si>
+  <si>
+    <t>interestThreshold</t>
+  </si>
+  <si>
+    <t>Interest:每满该金币阈值</t>
+  </si>
+  <si>
+    <t>interestGoldPer</t>
+  </si>
+  <si>
+    <t>Interest:每档获得金币</t>
+  </si>
+  <si>
+    <t>shopFoodSaleSlotCount</t>
+  </si>
+  <si>
+    <t>商店食物出售栏位数量</t>
+  </si>
+  <si>
+    <t>shopPassiveItemSaleSlotCount</t>
+  </si>
+  <si>
+    <t>商店被动道具出售栏位数量</t>
+  </si>
+  <si>
+    <t>shopActiveItemSaleSlotCount</t>
+  </si>
+  <si>
+    <t>商店主动道具出售栏位数量</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -49,86 +448,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -411,152 +1037,153 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="31.0769230769231" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="34.5384615384615" customWidth="1"/>
+    <col min="4" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>##var#column</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>initialGold</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>初始金币</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
         <v>9999</v>
       </c>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>initialInterestCap</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>利息节点单次最高可获得金币数</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>initialFoodAdjustCount</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>初始食物调整次数</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>interestThreshold</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Interest:每满该金币阈值</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>interestGoldPer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Interest:每档获得金币</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interestThreshold</t>
+          <t>initialActionRerollCount</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,30 +529,50 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Interest:每满该金币阈值</t>
+          <t>初始行动刷新次数</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>interestThreshold</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Interest:每满该金币阈值</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>interestGoldPer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Interest:每档获得金币</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -1,266 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="game_base" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
-  <si>
-    <t>##var#column</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>initialGold</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>初始金币</t>
-  </si>
-  <si>
-    <t>initialInterestCap</t>
-  </si>
-  <si>
-    <t>利息节点单次最高可获得金币数</t>
-  </si>
-  <si>
-    <t>initialFoodAdjustCount</t>
-  </si>
-  <si>
-    <t>初始食物调整次数</t>
-  </si>
-  <si>
-    <t>interestThreshold</t>
-  </si>
-  <si>
-    <t>Interest:每满该金币阈值</t>
-  </si>
-  <si>
-    <t>interestGoldPer</t>
-  </si>
-  <si>
-    <t>Interest:每档获得金币</t>
-  </si>
-  <si>
-    <t>initialActionRerollCount</t>
-  </si>
-  <si>
-    <t>初始行动刷新次数</t>
-  </si>
-  <si>
-    <t>shopFoodSaleSlotCount</t>
-  </si>
-  <si>
-    <t>商店食物出售栏位数量</t>
-  </si>
-  <si>
-    <t>shopPassiveItemSaleSlotCount</t>
-  </si>
-  <si>
-    <t>商店被动道具出售栏位数量</t>
-  </si>
-  <si>
-    <t>shopActiveItemSaleSlotCount</t>
-  </si>
-  <si>
-    <t>商店主动道具出售栏位数量</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -561,154 +472,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -762,11 +673,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1053,163 +1027,238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="31.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="34.5384615384615" customWidth="1"/>
-    <col min="4" max="6" width="22" customWidth="1"/>
+    <col width="31.0769230769231" customWidth="1" style="1" min="1" max="1"/>
+    <col width="22" customWidth="1" style="1" min="2" max="2"/>
+    <col width="34.5384615384615" customWidth="1" style="1" min="3" max="3"/>
+    <col width="22" customWidth="1" style="1" min="4" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var#column</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>initialGold</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>初始金币</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>initialInterestCap</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>利息节点单次最高可获得金币数</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>initialFoodAdjustCount</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>初始食物调整次数</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>interestThreshold</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Interest:每满该金币阈值</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>interestGoldPer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Interest:每档获得金币</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>initialActionRerollCount</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>初始行动刷新次数</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>shopFoodSaleSlotCount</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>商店食物出售栏位数量</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shopPassiveItemSaleSlotCount</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>商店被动道具出售栏位数量</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>shopActiveItemSaleSlotCount</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>商店主动道具出售栏位数量</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>foodFlavorLimit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>食物风味上限</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <v>9999</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="31.0769230769231" customWidth="1" style="1" min="1" max="1"/>
@@ -1258,6 +1258,70 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fragmentPackPrices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>碎片包按购买次数递增价格</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>deleteDishPrices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>删除菜品按删除次数递增价格</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>shopPriceFluctuationPct</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>商店食物/主动/被动道具基础价格随机浮动比例</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -1,289 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="game_base" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
-  <si>
-    <t>##var#column</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>initialGold</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>初始金币</t>
-  </si>
-  <si>
-    <t>initialInterestCap</t>
-  </si>
-  <si>
-    <t>利息节点单次最高可获得金币数</t>
-  </si>
-  <si>
-    <t>initialFoodAdjustCount</t>
-  </si>
-  <si>
-    <t>初始食物调整次数</t>
-  </si>
-  <si>
-    <t>interestThreshold</t>
-  </si>
-  <si>
-    <t>Interest:每满该金币阈值</t>
-  </si>
-  <si>
-    <t>interestGoldPer</t>
-  </si>
-  <si>
-    <t>Interest:每档获得金币</t>
-  </si>
-  <si>
-    <t>initialActionRerollCount</t>
-  </si>
-  <si>
-    <t>初始行动刷新次数</t>
-  </si>
-  <si>
-    <t>shopFoodSaleSlotCount</t>
-  </si>
-  <si>
-    <t>商店食物出售栏位数量</t>
-  </si>
-  <si>
-    <t>shopPassiveItemSaleSlotCount</t>
-  </si>
-  <si>
-    <t>商店被动道具出售栏位数量</t>
-  </si>
-  <si>
-    <t>shopActiveItemSaleSlotCount</t>
-  </si>
-  <si>
-    <t>商店主动道具出售栏位数量</t>
-  </si>
-  <si>
-    <t>foodFlavorLimit</t>
-  </si>
-  <si>
-    <t>食物风味上限</t>
-  </si>
-  <si>
-    <t>fragmentPackPrices</t>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
-    <t>碎片包按购买次数递增价格</t>
-  </si>
-  <si>
-    <t>30,45,60,80,100</t>
-  </si>
-  <si>
-    <t>deleteDishPrices</t>
-  </si>
-  <si>
-    <t>删除菜品按删除次数递增价格</t>
-  </si>
-  <si>
-    <t>20,25,30,40,50</t>
-  </si>
-  <si>
-    <t>shopPriceFluctuationPct</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>商店食物/主动/被动道具基础价格随机浮动比例</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -584,154 +472,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -787,11 +675,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1078,213 +1029,365 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="31.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="51.5384615384615" customWidth="1"/>
-    <col min="4" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
+    <col width="31.0769230769231" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="51.5384615384615" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" style="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var#column</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>initialGold</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>初始金币</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>initialInterestCap</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>利息节点单次最高可获得金币数</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>initialFoodAdjustCount</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>初始食物调整次数</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>interestThreshold</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Interest:每满该金币阈值</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>interestGoldPer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Interest:每档获得金币</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>initialActionRerollCount</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>初始行动刷新次数</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>baseActiveSlots</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>主动道具基础消耗槽数</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shopFoodSaleSlotCount</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>商店食物出售栏位数量</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>shopPassiveItemSaleSlotCount</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>商店被动道具出售栏位数量</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>shopActiveItemSaleSlotCount</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>商店主动道具出售栏位数量</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>foodFlavorLimit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>食物风味上限</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fragmentPackPrices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>碎片包按购买次数递增价格</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>30,45,60,80,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>deleteDishPrices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>删除菜品按删除次数递增价格</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>20,25,30,40,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>recipeBookPrices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>商店购买菜谱按购买次数递增价格</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>20,30,40,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>maxRecipeBookCount</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>菜谱最大数量（商店购买/获取菜谱上限）</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="1">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>shopPriceFluctuationPct</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>商店食物/主动/被动道具基础价格随机浮动比例</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>0.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>##var#column</t>
   </si>
@@ -51,12 +51,6 @@
   </si>
   <si>
     <t>利息节点单次最高可获得金币数</t>
-  </si>
-  <si>
-    <t>initialFoodAdjustCount</t>
-  </si>
-  <si>
-    <t>初始食物调整次数</t>
   </si>
   <si>
     <t>interestThreshold</t>
@@ -1258,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="31.0769230769231" customWidth="1"/>
@@ -1318,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1332,7 +1326,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1346,7 +1340,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1360,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1374,7 +1368,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1388,7 +1382,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1416,7 +1410,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1424,55 +1418,55 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="1">
-        <v>0.2</v>
+      <c r="D15">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1486,7 +1480,7 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1494,13 +1488,13 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1508,13 +1502,13 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1522,13 +1516,13 @@
         <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
         <v>43</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1536,13 +1530,13 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
       </c>
       <c r="D20">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1550,26 +1544,12 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
         <v>47</v>
       </c>
       <c r="D21">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22">
         <v>0.1</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -749,11 +749,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1260,8 +1257,7 @@
     <col min="1" max="1" width="31.0769230769231" style="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
     <col min="3" max="3" width="51.5384615384615" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="2" customWidth="1"/>
-    <col min="5" max="6" width="22" style="1" customWidth="1"/>
+    <col min="4" max="6" width="22" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1286,7 +1282,7 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>50</v>
       </c>
     </row>
@@ -1300,7 +1296,7 @@
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>30</v>
       </c>
     </row>
@@ -1314,7 +1310,7 @@
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>5</v>
       </c>
     </row>
@@ -1328,7 +1324,7 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1342,7 +1338,7 @@
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1356,7 +1352,7 @@
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>2</v>
       </c>
     </row>
@@ -1370,7 +1366,7 @@
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>3</v>
       </c>
     </row>
@@ -1384,7 +1380,7 @@
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>2</v>
       </c>
     </row>
@@ -1398,7 +1394,7 @@
       <c r="C10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>2</v>
       </c>
     </row>
@@ -1412,7 +1408,7 @@
       <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1426,8 +1422,8 @@
       <c r="C12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="3">
-        <v>1</v>
+      <c r="D12" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1440,7 +1436,7 @@
       <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1454,7 +1450,7 @@
       <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1497,7 +1493,7 @@
         <v>39</v>
       </c>
       <c r="D17" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1511,7 +1507,7 @@
         <v>41</v>
       </c>
       <c r="D18" s="1">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1566,7 +1562,7 @@
       <c r="C22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>0.1</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="Rbb3c16aeb16b4cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R525de735472a4609"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1493,6 +1493,20 @@
         <x:v>arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>initialHeartCount</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>开局爱心数量（同时初始化当前爱心与爱心上限）</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="Rbb3c16aeb16b4cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R3ee6f3e4c70a4cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R1f1bd1ef3fb240b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,18 +98,12 @@
     <x:t xml:space="preserve">碎片包按购买次数递增价格</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">30,45,60,80,100</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">deleteDishPrices</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">删除菜品按删除次数递增价格</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">20,25,30,40,50</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">shopPriceFluctuationPct</x:t>
   </x:si>
   <x:si>
@@ -164,6 +159,63 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">每次进入商店最多可删除食物次数（0=不限）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">serveCookiePityCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">连续出菜均为饼干达到该次数后，下一次优先非饼干（0=关闭）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">serveCookieDishIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(list#sep=,),string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">出菜保底认定为饼干的食物本体ID列表</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">经济</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">第一周获得的钱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">确定性溢价</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">每周行动次数</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">利息</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">食物</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">删除</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">格子</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">主动</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">被动传说</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">被动顶级</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">被动高级</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">被动普通</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -674,8 +726,9 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
@@ -686,7 +739,7 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -1139,358 +1192,516 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="51.53845977783203" style="1" customWidth="1"/>
-    <x:col min="4" max="6" width="22" style="1" customWidth="1"/>
-    <x:col min="7" max="16384" width="9" style="1" customWidth="0"/>
+    <x:col min="1" max="1" width="31.076923370361328" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="22" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="68.84615325927734" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="64.84615325927734" style="2" customWidth="1"/>
+    <x:col min="5" max="6" width="22" style="2" customWidth="1"/>
+    <x:col min="7" max="16384" width="9" style="2" customWidth="0"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="C1" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="A2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="C2" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D2" s="1">
+      <x:c r="D2" s="2">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1" t="s">
+      <x:c r="A3" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="B3" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="C3" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="1">
+      <x:c r="D3" s="2">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1" t="s">
+      <x:c r="A4" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="B4" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="C4" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D4" s="1">
+      <x:c r="D4" s="2">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="1" t="s">
+      <x:c r="A5" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="B5" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="C5" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D5" s="1">
+      <x:c r="D5" s="2">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="1" t="s">
+      <x:c r="A6" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="B6" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="C6" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D6" s="1">
+      <x:c r="D6" s="2">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="1" t="s">
+      <x:c r="A7" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="B7" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="C7" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D7" s="1">
+      <x:c r="D7" s="2">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="1" t="s">
+      <x:c r="A8" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
+      <x:c r="B8" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="C8" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D8" s="1">
+      <x:c r="D8" s="2">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="1" t="s">
+      <x:c r="A9" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="B9" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="C9" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="1">
+      <x:c r="D9" s="2">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="1" t="s">
+      <x:c r="A10" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="B10" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="C10" s="2" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D10" s="1">
+      <x:c r="D10" s="2">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="1" t="s">
+      <x:c r="A11" s="2" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="B11" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="C11" s="2" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D11" s="1">
+      <x:c r="D11" s="2">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="1" t="s">
+      <x:c r="A12" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="B12" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="C12" s="2" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D12" s="2">
+      <x:c r="D12" s="3">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="1" t="s">
+      <x:c r="A13" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="B13" s="2" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="C13" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="D13" s="2" t="str">
+        <x:f>_xlfn.TEXTJOIN(",",TRUE,Sheet1!J13:N13)</x:f>
+        <x:v>60,60,80,80,100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="B14" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="str">
+        <x:f>_xlfn.TEXTJOIN(",",TRUE,Sheet1!J12:M12)</x:f>
+        <x:v>40,50,60,80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D15" s="2">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D16" s="2">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D17" s="2">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D18" s="2">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D19" s="2">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D20" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D21" s="2">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="2" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D22" s="4">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="2" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D23" s="2">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B24" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D24" s="5">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>shopFragmentPackPurchaseLimit</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>每次进入商店最多可购买碎片包次数（0=不限）</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultColWidth="9.230769157409668" defaultRowHeight="16.799999237060547"/>
+  <x:sheetData>
+    <x:row r="4">
+      <x:c r="C4" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="E6" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F6"/>
+      <x:c r="G6">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="I6" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K6">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="M6" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O6">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="E8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="E12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F12"/>
+      <x:c r="I12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J12">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K12">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M12">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="I13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J13">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K13">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L13">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="M13">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="N13">
+        <x:v>100</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>32</x:v>
+      <x:c r="I14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J14">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K14"/>
+      <x:c r="O14">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="1">
-        <x:v>0.2</x:v>
+      <x:c r="I15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J15">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K15" s="1">
+        <x:v>0.07</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D16" s="1">
-        <x:v>3</x:v>
+      <x:c r="I16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J16">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K16" s="1">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:f>SUMPRODUCT(J15:J18,K15:K18)</x:f>
+        <x:v>83.60000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D17" s="1">
-        <x:v>100</x:v>
+      <x:c r="I17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J17">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K17" s="1">
+        <x:v>0.42</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="1" t="s">
+      <x:c r="I18" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J18">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D18" s="1">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D19" s="1">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D20" s="1">
-        <x:v>0.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D21" s="1">
-        <x:v>1.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D22" s="3">
-        <x:v>0.1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B23" s="4" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D23" s="4">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>serveCookiePityCount</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>连续出菜均为饼干达到该次数后，下一次优先非饼干（0=关闭）</x:v>
-      </x:c>
-      <x:c r="D24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>serveCookieDishIds</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>(list#sep=,),string</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>出菜保底认定为饼干的食物本体ID列表</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:v>
+      <x:c r="K18" s="1">
+        <x:v>0.38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R4318df76e74e41c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Rfd9deec08db84954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R6c3261fcafbb415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Rbaec92c4d2734ddd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1291,8 +1291,8 @@
       <x:c r="C7" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D7" s="2">
-        <x:v>2</x:v>
+      <x:c r="D7" s="2" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8">

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R6c3261fcafbb415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Rbaec92c4d2734ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="Rb8d8debd203a463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Rd3b300c3209342c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56,9 +56,6 @@
     <x:t xml:space="preserve">baseActiveSlots</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">主动道具基础消耗槽数</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">shopFoodSaleSlotCount</x:t>
   </x:si>
   <x:si>
@@ -68,15 +65,9 @@
     <x:t xml:space="preserve">shopPassiveItemSaleSlotCount</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">商店被动道具出售栏位数量</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">shopActiveItemSaleSlotCount</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">商店主动道具出售栏位数量</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">foodFlavorLimit</x:t>
   </x:si>
   <x:si>
@@ -86,9 +77,6 @@
     <x:t xml:space="preserve">foodDeleteCount</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">美食战斗每局可丢弃出餐食物次数</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fragmentPackPrices</x:t>
   </x:si>
   <x:si>
@@ -101,18 +89,12 @@
     <x:t xml:space="preserve">deleteDishPrices</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">删除菜品按删除次数递增价格</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">shopPriceFluctuationPct</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">float</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">商店食物/主动/被动道具基础价格随机浮动比例</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">actionChoiceCount</x:t>
   </x:si>
   <x:si>
@@ -120,9 +102,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">hiddenScoreDistanceFloor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">隐藏分距离加权下限（菜品/道具/碎片随机池共用）</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">minimumRandomWeight</x:t>
@@ -1288,8 +1267,8 @@
       <x:c r="B7" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>15</x:v>
+      <x:c r="C7" s="2" t="str">
+        <x:v>消耗品栏基础栏位数</x:v>
       </x:c>
       <x:c r="D7" s="2" t="n">
         <x:v>4</x:v>
@@ -1297,13 +1276,13 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="2">
         <x:v>3</x:v>
@@ -1311,13 +1290,13 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>19</x:v>
+      <x:c r="C9" s="2" t="str">
+        <x:v>商店装饰品出售栏位数量</x:v>
       </x:c>
       <x:c r="D9" s="2">
         <x:v>2</x:v>
@@ -1325,13 +1304,13 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>21</x:v>
+      <x:c r="C10" s="2" t="str">
+        <x:v>商店消耗品出售栏位数量</x:v>
       </x:c>
       <x:c r="D10" s="2">
         <x:v>2</x:v>
@@ -1339,13 +1318,13 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D11" s="2">
         <x:v>1</x:v>
@@ -1353,13 +1332,13 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>25</x:v>
+      <x:c r="C12" s="2" t="str">
+        <x:v>经营挑战每局可丢弃出菜食物次数</x:v>
       </x:c>
       <x:c r="D12" s="3">
         <x:v>2</x:v>
@@ -1367,13 +1346,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
         <x:f>_xlfn.TEXTJOIN(",",TRUE,Sheet1!J13:N13)</x:f>
@@ -1382,13 +1361,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="str">
+        <x:v>删除食物按删除次数递增价格</x:v>
       </x:c>
       <x:c r="D14" s="2" t="str">
         <x:f>_xlfn.TEXTJOIN(",",TRUE,Sheet1!J12:M12)</x:f>
@@ -1397,13 +1376,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="str">
+        <x:v>商店食物/消耗品/装饰品基础价格随机浮动比例</x:v>
       </x:c>
       <x:c r="D15" s="2">
         <x:v>0.2</x:v>
@@ -1411,13 +1390,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D16" s="2">
         <x:v>3</x:v>
@@ -1425,13 +1404,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C17" s="2" t="s">
-        <x:v>37</x:v>
+      <x:c r="C17" s="2" t="str">
+        <x:v>隐藏分距离加权下限（食物/装饰品和消耗品/碎片随机池共用）</x:v>
       </x:c>
       <x:c r="D17" s="2">
         <x:v>100</x:v>
@@ -1439,13 +1418,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="2" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="D18" s="2">
         <x:v>1</x:v>
@@ -1453,13 +1432,13 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D19" s="2">
         <x:v>1</x:v>
@@ -1467,13 +1446,13 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D20" s="2">
         <x:v>0.5</x:v>
@@ -1481,13 +1460,13 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="2">
         <x:v>1.5</x:v>
@@ -1495,13 +1474,13 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D22" s="4">
         <x:v>0.1</x:v>
@@ -1509,13 +1488,13 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D23" s="2">
         <x:v>1</x:v>
@@ -1523,13 +1502,13 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C24" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D24" s="5">
         <x:v>4</x:v>
@@ -1537,16 +1516,16 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D25" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1588,25 +1567,25 @@
   <x:sheetData>
     <x:row r="4">
       <x:c r="C4" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="E6" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F6"/>
       <x:c r="G6">
         <x:v>280</x:v>
       </x:c>
       <x:c r="I6" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="M6" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O6">
         <x:v>7</x:v>
@@ -1614,16 +1593,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="E8" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="E12" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F12"/>
       <x:c r="I12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J12">
         <x:v>40</x:v>
@@ -1640,7 +1619,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="I13" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J13">
         <x:v>60</x:v>
@@ -1660,7 +1639,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="I14" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J14">
         <x:v>40</x:v>
@@ -1672,7 +1651,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="I15" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J15">
         <x:v>240</x:v>
@@ -1683,7 +1662,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="I16" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J16">
         <x:v>150</x:v>
@@ -1698,7 +1677,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="I17" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J17">
         <x:v>80</x:v>
@@ -1709,7 +1688,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="I18" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J18">
         <x:v>40</x:v>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="Rff94d71a619f4b89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R2b81c1c218b74ee6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R1544f5bbc33040f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Re0e0c1be964a4607"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1600,6 +1600,62 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>slotEmptyWeight</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>抽奖机空奖权重</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>slotFreeSpins</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>每个抽奖机节点的免费抽奖次数</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>slotPaidCost</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>抽奖机免费次数用完后的单次金币价格</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>slotMaxSpins</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>每个抽奖机节点最多抽奖次数</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,194 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R1544f5bbc33040f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Re0e0c1be964a4607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R5f875001fbee4037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R64e10758e43d4aa6"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">##var#column</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">initialGold</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">初始金币</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">initialInterestCap</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">利息节点单次最高可获得金币数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">interestThreshold</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interest:每满该金币阈值</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">interestGoldPer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interest:每档获得金币</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">initialActionRerollCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">初始行动刷新次数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">baseActiveSlots</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">消耗品栏基础栏位数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">shopFoodSaleSlotCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">商店食物出售栏位数量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">shopPassiveItemSaleSlotCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">商店装饰品出售栏位数量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">shopActiveItemSaleSlotCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">商店消耗品出售栏位数量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">foodFlavorLimit</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">食物风味上限</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">foodDeleteCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">经营挑战每局可丢弃出菜食物次数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fragmentPackPrices</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(list#sep=,),int</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">碎片包按购买次数递增价格</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">deleteDishPrices</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">删除食物按删除次数递增价格</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">shopPriceFluctuationPct</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">float</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">商店食物/消耗品/装饰品基础价格随机浮动比例</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">actionChoiceCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">行动随机候选数量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">hiddenScoreDistanceFloor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">隐藏分距离加权下限（食物/装饰品和消耗品/碎片随机池共用）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">minimumRandomWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">随机池修正后权重的最小正值</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">defaultRandomWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">随机池基础权重未配置或非正数时的默认值</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">randomServeMultiplierMin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">黑暗料理随机上菜倍率下限</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">randomServeMultiplierMax</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">黑暗料理随机上菜倍率上限</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">randomServeMultiplierStep</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">黑暗料理随机上菜倍率步长</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">shopDeleteDishLimit</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每次进入商店最多可删除食物次数（0=不限）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">serveCookiePityCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">连续出菜均为饼干达到该次数后，下一次优先非饼干（0=关闭）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">serveCookieDishIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(list#sep=,),string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">出菜保底认定为饼干的食物本体ID列表</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">shopFragmentPackPurchaseLimit</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每次进入商店最多可购买碎片包次数（0=不限）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">initialHeartCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">开局爱心数量（同时初始化当前爱心与爱心上限）</x:t>
-  </x:si>
   <x:si>
     <x:t xml:space="preserve">经济</x:t>
   </x:si>
@@ -1210,379 +1030,378 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="2" t="s">
+      <x:c r="A1" s="2" t="str">
+        <x:v>##var#column</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="D1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>initialGold</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>初始金币</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="str">
+        <x:v>initialInterestCap</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>利息节点单次最高可获得金币数</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="str">
+        <x:v>interestThreshold</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="str">
+        <x:v>Interest:每满该金币阈值</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2" t="str">
+        <x:v>interestGoldPer</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>Interest:每档获得金币</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="str">
+        <x:v>initialActionRerollCount</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="str">
+        <x:v>初始行动刷新次数</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="str">
+        <x:v>baseActiveSlots</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>消耗品栏基础栏位数</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="str">
+        <x:v>shopFoodSaleSlotCount</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>商店食物出售栏位数量</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="str">
+        <x:v>shopPassiveItemSaleSlotCount</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>商店装饰品出售栏位数量</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="str">
+        <x:v>shopActiveItemSaleSlotCount</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>商店消耗品出售栏位数量</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="str">
+        <x:v>foodFlavorLimit</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>食物风味上限</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="str">
+        <x:v>foodDeleteCount</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>经营挑战每局可丢弃出菜食物次数</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="s">
+    <x:row r="13">
+      <x:c r="A13" s="2" t="str">
+        <x:v>fragmentPackPrices</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="str">
+        <x:v>(list#sep=,),int</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="str">
+        <x:v>碎片包按购买次数递增价格</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="str">
+        <x:v>60,60,80,80,100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="str">
+        <x:v>deleteDishPrices</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="str">
+        <x:v>(list#sep=,),int</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="str">
+        <x:v>删除食物按删除次数递增价格</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="str">
+        <x:v>40,50,60,80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="str">
+        <x:v>shopPriceFluctuationPct</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="str">
+        <x:v>商店食物/消耗品/装饰品基础价格随机浮动比例</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="str">
+        <x:v>actionChoiceCount</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="str">
+        <x:v>行动随机候选数量</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="s">
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2" t="str">
+        <x:v>hiddenScoreDistanceFloor</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="str">
+        <x:v>隐藏分距离加权下限（食物/装饰品和消耗品/碎片随机池共用）</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2" t="str">
+        <x:v>minimumRandomWeight</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="str">
+        <x:v>随机池修正后权重的最小正值</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2" t="str">
+        <x:v>defaultRandomWeight</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="str">
+        <x:v>随机池基础权重未配置或非正数时的默认值</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2" t="str">
+        <x:v>randomServeMultiplierMin</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="str">
+        <x:v>黑暗料理随机上菜倍率下限</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2" t="str">
+        <x:v>randomServeMultiplierMax</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="str">
+        <x:v>黑暗料理随机上菜倍率上限</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2" t="str">
+        <x:v>randomServeMultiplierStep</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C22" s="2" t="str">
+        <x:v>黑暗料理随机上菜倍率步长</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2" t="str">
+        <x:v>shopDeleteDishLimit</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C23" s="2" t="str">
+        <x:v>每次进入商店最多可删除食物次数（0=不限）</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2" t="str">
+        <x:v>serveCookiePityCount</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="str">
+        <x:v>连续出菜均为饼干达到该次数后，下一次优先非饼干（0=关闭）</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="2">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="2">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="2">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="2">
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2" t="str">
+        <x:v>serveCookieDishIds</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="str">
+        <x:v>(list#sep=,),string</x:v>
+      </x:c>
+      <x:c r="C25" s="2" t="str">
+        <x:v>出菜保底认定为饼干的食物本体ID列表</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="str">
+        <x:v>arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>shopFragmentPackPurchaseLimit</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>每次进入商店最多可购买碎片包次数（0=不限）</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="2">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="2">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="2">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="2">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="2">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D11" s="2">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D12" s="3">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="str">
-        <x:f>_xlfn.TEXTJOIN(",",TRUE,Sheet1!J13:N13)</x:f>
-        <x:v>60,60,80,80,100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="str">
-        <x:f>_xlfn.TEXTJOIN(",",TRUE,Sheet1!J12:M12)</x:f>
-        <x:v>40,50,60,80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="2" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D15" s="2">
-        <x:v>0.2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B16" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D16" s="2">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B17" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D17" s="2">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B18" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D18" s="2">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B19" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D19" s="2">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B20" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D20" s="2">
-        <x:v>0.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B21" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C21" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D21" s="2">
-        <x:v>1.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B22" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C22" s="2" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D22" s="4">
-        <x:v>0.1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B23" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="2" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D23" s="2">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="2" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B24" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="2" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D24" s="2">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="2" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B25" s="2" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C25" s="2" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D25" s="2" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B26" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D26">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="27">
-      <x:c r="A27" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B27" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D27">
+      <x:c r="A27" t="str">
+        <x:v>initialHeartCount</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>开局爱心数量（同时初始化当前爱心与爱心上限）</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -1602,59 +1421,51 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>slotEmptyWeight</x:v>
+        <x:v>slotFreeSpins</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>float</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>抽奖机空奖权重</x:v>
+        <x:v>每个抽奖机节点的免费抽奖次数</x:v>
       </x:c>
       <x:c r="D29" t="n">
-        <x:v>40</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>slotFreeSpins</x:v>
+        <x:v>slotPaidCost</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>每个抽奖机节点的免费抽奖次数</x:v>
+        <x:v>抽奖机免费次数用完后的单次金币价格</x:v>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>slotPaidCost</x:v>
+        <x:v>slotMaxSpins</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>抽奖机免费次数用完后的单次金币价格</x:v>
+        <x:v>每个抽奖机节点最多抽奖次数</x:v>
       </x:c>
       <x:c r="D31" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>slotMaxSpins</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>每个抽奖机节点最多抽奖次数</x:v>
-      </x:c>
-      <x:c r="D32" t="n">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1667,24 +1478,24 @@
   <x:sheetData>
     <x:row r="4">
       <x:c r="C4" t="s">
-        <x:v>60</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="E6" t="s">
-        <x:v>61</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G6">
         <x:v>280</x:v>
       </x:c>
       <x:c r="I6" t="s">
-        <x:v>62</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K6">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="M6" t="s">
-        <x:v>63</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="O6">
         <x:v>7</x:v>
@@ -1692,15 +1503,15 @@
     </x:row>
     <x:row r="8">
       <x:c r="E8" t="s">
-        <x:v>64</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="E12" t="s">
-        <x:v>65</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I12" t="s">
-        <x:v>66</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J12">
         <x:v>40</x:v>
@@ -1717,7 +1528,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="I13" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J13">
         <x:v>60</x:v>
@@ -1737,7 +1548,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="I14" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J14">
         <x:v>40</x:v>
@@ -1748,7 +1559,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="I15" t="s">
-        <x:v>69</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J15">
         <x:v>240</x:v>
@@ -1759,7 +1570,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="I16" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J16">
         <x:v>150</x:v>
@@ -1774,7 +1585,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="I17" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J17">
         <x:v>80</x:v>
@@ -1785,7 +1596,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="I18" t="s">
-        <x:v>72</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J18">
         <x:v>40</x:v>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R5f875001fbee4037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R64e10758e43d4aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_base" sheetId="1" r:id="R3ef6c8915fb94c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R48a356b8f12442c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1239,41 +1239,41 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2" t="str">
-        <x:v>actionChoiceCount</x:v>
+        <x:v>hiddenScoreDistanceFloor</x:v>
       </x:c>
       <x:c r="B16" s="2" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C16" s="2" t="str">
-        <x:v>行动随机候选数量</x:v>
+        <x:v>隐藏分距离加权下限（食物/装饰品和消耗品/碎片随机池共用）</x:v>
       </x:c>
       <x:c r="D16" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="str">
-        <x:v>hiddenScoreDistanceFloor</x:v>
+        <x:v>minimumRandomWeight</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="C17" s="2" t="str">
-        <x:v>隐藏分距离加权下限（食物/装饰品和消耗品/碎片随机池共用）</x:v>
+        <x:v>随机池修正后权重的最小正值</x:v>
       </x:c>
       <x:c r="D17" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="str">
-        <x:v>minimumRandomWeight</x:v>
+        <x:v>defaultRandomWeight</x:v>
       </x:c>
       <x:c r="B18" s="2" t="str">
         <x:v>float</x:v>
       </x:c>
       <x:c r="C18" s="2" t="str">
-        <x:v>随机池修正后权重的最小正值</x:v>
+        <x:v>随机池基础权重未配置或非正数时的默认值</x:v>
       </x:c>
       <x:c r="D18" s="2" t="n">
         <x:v>1</x:v>
@@ -1281,185 +1281,177 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="str">
-        <x:v>defaultRandomWeight</x:v>
+        <x:v>randomServeMultiplierMin</x:v>
       </x:c>
       <x:c r="B19" s="2" t="str">
         <x:v>float</x:v>
       </x:c>
       <x:c r="C19" s="2" t="str">
-        <x:v>随机池基础权重未配置或非正数时的默认值</x:v>
+        <x:v>黑暗料理随机上菜倍率下限</x:v>
       </x:c>
       <x:c r="D19" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="str">
-        <x:v>randomServeMultiplierMin</x:v>
+        <x:v>randomServeMultiplierMax</x:v>
       </x:c>
       <x:c r="B20" s="2" t="str">
         <x:v>float</x:v>
       </x:c>
       <x:c r="C20" s="2" t="str">
-        <x:v>黑暗料理随机上菜倍率下限</x:v>
+        <x:v>黑暗料理随机上菜倍率上限</x:v>
       </x:c>
       <x:c r="D20" s="2" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="str">
-        <x:v>randomServeMultiplierMax</x:v>
+        <x:v>randomServeMultiplierStep</x:v>
       </x:c>
       <x:c r="B21" s="2" t="str">
         <x:v>float</x:v>
       </x:c>
       <x:c r="C21" s="2" t="str">
-        <x:v>黑暗料理随机上菜倍率上限</x:v>
+        <x:v>黑暗料理随机上菜倍率步长</x:v>
       </x:c>
       <x:c r="D21" s="2" t="n">
-        <x:v>1.5</x:v>
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="str">
-        <x:v>randomServeMultiplierStep</x:v>
+        <x:v>shopDeleteDishLimit</x:v>
       </x:c>
       <x:c r="B22" s="2" t="str">
-        <x:v>float</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="C22" s="2" t="str">
-        <x:v>黑暗料理随机上菜倍率步长</x:v>
+        <x:v>每次进入商店最多可删除食物次数（0=不限）</x:v>
       </x:c>
       <x:c r="D22" s="4" t="n">
-        <x:v>0.1</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="str">
-        <x:v>shopDeleteDishLimit</x:v>
+        <x:v>serveCookiePityCount</x:v>
       </x:c>
       <x:c r="B23" s="2" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C23" s="2" t="str">
-        <x:v>每次进入商店最多可删除食物次数（0=不限）</x:v>
+        <x:v>连续出菜均为饼干达到该次数后，下一次优先非饼干（0=关闭）</x:v>
       </x:c>
       <x:c r="D23" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="str">
-        <x:v>serveCookiePityCount</x:v>
+        <x:v>serveCookieDishIds</x:v>
       </x:c>
       <x:c r="B24" s="2" t="str">
-        <x:v>int</x:v>
+        <x:v>(list#sep=,),string</x:v>
       </x:c>
       <x:c r="C24" s="2" t="str">
-        <x:v>连续出菜均为饼干达到该次数后，下一次优先非饼干（0=关闭）</x:v>
-      </x:c>
-      <x:c r="D24" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>出菜保底认定为饼干的食物本体ID列表</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="str">
+        <x:v>arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="str">
-        <x:v>serveCookieDishIds</x:v>
+        <x:v>shopFragmentPackPurchaseLimit</x:v>
       </x:c>
       <x:c r="B25" s="2" t="str">
-        <x:v>(list#sep=,),string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="C25" s="2" t="str">
-        <x:v>出菜保底认定为饼干的食物本体ID列表</x:v>
-      </x:c>
-      <x:c r="D25" s="2" t="str">
-        <x:v>arrow_cookie_1,arrow_cookie_2,arrow_cookie_3,arrow_cookie_4</x:v>
+        <x:v>每次进入商店最多可购买碎片包次数（0=不限）</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>shopFragmentPackPurchaseLimit</x:v>
+        <x:v>initialHeartCount</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>每次进入商店最多可购买碎片包次数（0=不限）</x:v>
+        <x:v>开局爱心数量（同时初始化当前爱心与爱心上限）</x:v>
       </x:c>
       <x:c r="D26" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>initialHeartCount</x:v>
+        <x:v>totalWeeks</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>开局爱心数量（同时初始化当前爱心与爱心上限）</x:v>
+        <x:v>一局游戏总周数</x:v>
       </x:c>
       <x:c r="D27" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>totalWeeks</x:v>
+        <x:v>slotFreeSpins</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>一局游戏总周数</x:v>
+        <x:v>每个抽奖机节点的免费抽奖次数</x:v>
       </x:c>
       <x:c r="D28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>slotFreeSpins</x:v>
+        <x:v>slotPaidCost</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>每个抽奖机节点的免费抽奖次数</x:v>
+        <x:v>抽奖机免费次数用完后的单次金币价格</x:v>
       </x:c>
       <x:c r="D29" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>slotPaidCost</x:v>
+        <x:v>slotMaxSpins</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>抽奖机免费次数用完后的单次金币价格</x:v>
+        <x:v>每个抽奖机节点最多抽奖次数</x:v>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>slotMaxSpins</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>每个抽奖机节点最多抽奖次数</x:v>
-      </x:c>
-      <x:c r="D31" t="n">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -1701,7 +1701,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:4">

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -104,7 +104,7 @@
     <t>碎片包按购买次数递增价格</t>
   </si>
   <si>
-    <t>60,60,80,80,100</t>
+    <t>60,80,100,120</t>
   </si>
   <si>
     <t>deleteDishPrices</t>
@@ -113,7 +113,7 @@
     <t>删除食物按删除次数递增价格</t>
   </si>
   <si>
-    <t>40,50,60,80</t>
+    <t>50,70,90,100</t>
   </si>
   <si>
     <t>shopPriceFluctuationPct</t>
@@ -1407,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1785,7 +1785,7 @@
         <v>65</v>
       </c>
       <c r="D29" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/GourmetProject/GameConfig/Datas/game_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/game_base.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
   <si>
     <t>##var#column</t>
   </si>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t>主流派最低占比</t>
-  </si>
-  <si>
-    <t>0.45</t>
   </si>
   <si>
     <t>archetypePrimaryMinLead</t>
@@ -1785,7 +1782,7 @@
         <v>65</v>
       </c>
       <c r="D29" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1812,33 +1809,33 @@
       <c r="C31" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>70</v>
+      <c r="D31" s="3">
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D33" s="3">
         <v>2</v>
@@ -1858,24 +1855,24 @@
   <sheetData>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="5:15">
       <c r="E6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G6">
         <v>280</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K6">
         <v>1.2</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1883,15 +1880,15 @@
     </row>
     <row r="8" spans="5:5">
       <c r="E8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="5:13">
       <c r="E12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s">
         <v>81</v>
-      </c>
-      <c r="I12" t="s">
-        <v>82</v>
       </c>
       <c r="J12">
         <v>40</v>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="13" spans="9:14">
       <c r="I13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J13">
         <v>60</v>
@@ -1928,7 +1925,7 @@
     </row>
     <row r="14" spans="9:15">
       <c r="I14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14">
         <v>40</v>
@@ -1939,7 +1936,7 @@
     </row>
     <row r="15" spans="9:11">
       <c r="I15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J15">
         <v>240</v>
@@ -1950,7 +1947,7 @@
     </row>
     <row r="16" spans="9:13">
       <c r="I16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J16">
         <v>150</v>
@@ -1965,7 +1962,7 @@
     </row>
     <row r="17" spans="9:11">
       <c r="I17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J17">
         <v>80</v>
@@ -1976,7 +1973,7 @@
     </row>
     <row r="18" spans="9:11">
       <c r="I18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>40</v>
